--- a/artfynd/A 3412-2022 artfynd.xlsx
+++ b/artfynd/A 3412-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110941056</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98778</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550516</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7260583</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3412-2022 artfynd.xlsx
+++ b/artfynd/A 3412-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3412-2022 artfynd.xlsx
+++ b/artfynd/A 3412-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110941056</v>
+        <v>110941066</v>
       </c>
       <c r="B2" t="n">
-        <v>98902</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2082</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsrör</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calamagrostis chalybaea</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laest.) Fr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550516</v>
+        <v>550560</v>
       </c>
       <c r="R2" t="n">
-        <v>7260583</v>
+        <v>7260655</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110941108</v>
+        <v>110940963</v>
       </c>
       <c r="B3" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550540.4331840959</v>
+        <v>550560</v>
       </c>
       <c r="R3" t="n">
-        <v>7260590.658617545</v>
+        <v>7260652</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110940991</v>
+        <v>110941056</v>
       </c>
       <c r="B4" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>2082</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsrör</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Calamagrostis chalybaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Laest.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550540.4331840959</v>
+        <v>550516</v>
       </c>
       <c r="R4" t="n">
-        <v>7260590.658617545</v>
+        <v>7260583</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +993,978 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110941057</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>550524</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7260621</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110941058</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7260629</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110941059</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100387</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsrör</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Calamagrostis chalybaea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laest.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>550562</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7260648</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110941108</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>550540</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7260591</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110940979</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>550497</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7260602</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110940991</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>550540</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7260591</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:58</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110941123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>550524</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7260621</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110941124</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>550539</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7260629</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110941125</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98137</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Abraham-Persbäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>550560</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7260647</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
